--- a/data/trans_orig/P1435_2011_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1435_2011_2023-Habitat-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>697099</t>
+          <t>695132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>663995</t>
+          <t>663861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>684167</t>
+          <t>683649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1365005</t>
+          <t>1365114</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1385217</t>
+          <t>1385558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33055</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013184</t>
+          <t>1013650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>973524</t>
+          <t>973457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1001017</t>
+          <t>1000391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1990842</t>
+          <t>1991267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2018142</t>
+          <t>2018551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31167</t>
+          <t>31793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58660</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59289</t>
+          <t>58864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>748732</t>
+          <t>747569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>756570</t>
+          <t>756578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>738298</t>
+          <t>736867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>758925</t>
+          <t>759318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1490135</t>
+          <t>1490189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1512594</t>
+          <t>1513734</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38876</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>938060</t>
+          <t>938294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>946766</t>
+          <t>946758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1003805</t>
+          <t>1003714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1027673</t>
+          <t>1028351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1947688</t>
+          <t>1949072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1973195</t>
+          <t>1972522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>48187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51952</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3407438</t>
+          <t>3407724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3420946</t>
+          <t>3420866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3407965</t>
+          <t>3406722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3453096</t>
+          <t>3451374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6823216</t>
+          <t>6822437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6870768</t>
+          <t>6870771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150344</t>
+          <t>151587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114320</t>
+          <t>114317</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>162651</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3351,32 +3351,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3386,32 +3386,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>47946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>72053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3421,32 +3421,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>64704</t>
+          <t>69285</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>57870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79204</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -3464,32 +3464,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>626199</t>
+          <t>680766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>618987</t>
+          <t>673450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>630345</t>
+          <t>685292</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3499,32 +3499,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>619908</t>
+          <t>673380</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607635</t>
+          <t>660669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>629547</t>
+          <t>684776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3534,32 +3534,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1246107</t>
+          <t>1354146</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1231607</t>
+          <t>1339051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1257345</t>
+          <t>1365561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3577,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3612,17 +3612,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3807,32 +3807,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3842,32 +3842,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84405</t>
+          <t>94502</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>79615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98668</t>
+          <t>110527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3877,32 +3877,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>111732</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>95259</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122325</t>
+          <t>130190</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3920,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1176763</t>
+          <t>1031687</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1167390</t>
+          <t>1021785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1186494</t>
+          <t>1038989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3955,32 +3955,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>872675</t>
+          <t>975306</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>858412</t>
+          <t>959281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>886088</t>
+          <t>990193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3990,32 +3990,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2049437</t>
+          <t>2006993</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2027619</t>
+          <t>1988535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2085551</t>
+          <t>2023466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -4033,17 +4033,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4068,17 +4068,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957080</t>
+          <t>1069808</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957080</t>
+          <t>1069808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957080</t>
+          <t>1069808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149944</t>
+          <t>2118725</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149944</t>
+          <t>2118725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149944</t>
+          <t>2118725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>262464</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>57958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>577648</t>
+          <t>88921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4333,32 +4333,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>268939</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>738883</t>
+          <t>97215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4376,17 +4376,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>696491</t>
+          <t>793829</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689071</t>
+          <t>786575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700043</t>
+          <t>798288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4411,32 +4411,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>669464</t>
+          <t>738568</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>354280</t>
+          <t>721224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863991</t>
+          <t>752187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4446,32 +4446,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1365954</t>
+          <t>1532397</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>896010</t>
+          <t>1514147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1566473</t>
+          <t>1547177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>931928</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931928</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>931928</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4559,17 +4559,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1634893</t>
+          <t>1611362</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1634893</t>
+          <t>1611362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1634893</t>
+          <t>1611362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4719,32 +4719,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4754,32 +4754,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105237</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>93358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127126</t>
+          <t>125915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4789,32 +4789,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>129997</t>
+          <t>133331</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107031</t>
+          <t>114744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154119</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -4832,32 +4832,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>900995</t>
+          <t>963952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>885311</t>
+          <t>950228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>910362</t>
+          <t>973409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>985778</t>
+          <t>1007802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>963889</t>
+          <t>990206</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1009231</t>
+          <t>1022763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4902,32 +4902,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1886774</t>
+          <t>1971755</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1862652</t>
+          <t>1950006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1909740</t>
+          <t>1990342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4945,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1091015</t>
+          <t>1116121</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1091015</t>
+          <t>1116121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1091015</t>
+          <t>1116121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5015,17 +5015,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2016771</t>
+          <t>2105086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2016771</t>
+          <t>2105086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2016771</t>
+          <t>2105086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5175,27 +5175,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5210,32 +5210,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>310448</t>
+          <t>307501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1046860</t>
+          <t>364220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5245,32 +5245,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>358827</t>
+          <t>358755</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1338126</t>
+          <t>430079</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5288,22 +5288,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3400448</t>
+          <t>3470234</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3381644</t>
+          <t>3452952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3417196</t>
+          <t>3485203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5323,32 +5323,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3147824</t>
+          <t>3395057</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2608533</t>
+          <t>3364576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3344945</t>
+          <t>3421295</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5358,32 +5358,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6548273</t>
+          <t>6865290</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5774293</t>
+          <t>6828525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6753592</t>
+          <t>6899849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5401,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
